--- a/kawasaki_project/05_試算・管理シート/川崎町_第10期_計画見込量_中長期・保険料内訳_R8.10.17.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_第10期_計画見込量_中長期・保険料内訳_R8.10.17.xlsx
@@ -54,7 +54,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,11 +91,6 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -109,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,9 +124,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -543,7 +535,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>令和17年度・令和22年度の給付費を持つ22サービス。算定式と、令和7年度実績からの伸びを添えています。</t>
+          <t>令和17年度・令和22年度の給付費を持つ37サービス。算定式と、令和7年度実績からの伸びを添えています。</t>
         </is>
       </c>
     </row>
@@ -633,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -659,7 +651,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22サービス。算定式は第10期計画期間と同じです。
+          <t>37サービス。算定式は第10期計画期間と同じです。
 　見込量(年,要介護度) ＝ 令和7年度実績(要介護度) × 認定者数(年,要介護度) ÷ 認定者数(令和8年度,要介護度)
 認定者数は地域包括ケア「見える化」システムの推計値（性別・年齢5歳階級別・要介護度別）によります。サービス利用率・1人1月あたりの利用回（日）数・単価は令和7年度の水準で据え置いています。
 ⚠ **介護予防給付のサービスは、サービスごとの長期推計を行っていないため「─」としています**（素案 9-1 の注のとおり）。「未実施」を「適合」に丸めていません。</t>
@@ -2050,12 +2042,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>居宅サービス</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護</t>
+          <t>短期入所療養介護（介護老人保健施設）</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2069,287 +2061,287 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>389</v>
+        <v>8614</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>437</v>
+        <v>8780</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>490</v>
+        <v>9668</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>508</v>
+        <v>10579</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>1.260倍</t>
+          <t>1.122倍</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>1.306倍</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+          <t>1.228倍</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>居宅サービス</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護</t>
+          <t>短期入所療養介護（介護老人保健施設）</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
+          <t>回（日）数</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>1.124倍</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>1.228倍</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>居宅サービス</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（介護老人保健施設）</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
           <t>利用者数</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>1.250倍</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>1.250倍</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>地域密着型サービス</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>夜間対応型訪問介護</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="E34" s="4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>1.131倍</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>1.238倍</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>居宅サービス</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>特定福祉用具購入費</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>給付費</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>千円／年</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>地域密着型サービス</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>夜間対応型訪問介護</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="n">
+        <v>575</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>576</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>678</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>1.113倍</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>1.179倍</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>居宅サービス</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>特定福祉用具購入費</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>利用者数</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>地域密着型サービス</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>地域密着型通所介護</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="E36" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>1.125倍</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>1.188倍</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>居宅サービス</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>住宅改修</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>給付費</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>千円／年</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n">
-        <v>377</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>408</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>457</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>474</v>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>1.212倍</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>1.257倍</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>地域密着型サービス</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>地域密着型通所介護</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>回（日）数</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>1.207倍</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>1.256倍</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+      <c r="E37" s="5" t="n">
+        <v>1009</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1029</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>1146</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>1.136倍</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>1.193倍</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>居宅サービス</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>地域密着型通所介護</t>
+          <t>住宅改修</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2363,42 +2355,42 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F38" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="4" t="n">
-        <v>1.1</v>
-      </c>
       <c r="H38" s="4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>1.222倍</t>
+          <t>1.250倍</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>1.333倍</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+          <t>1.250倍</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>居宅サービス</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護（介護予防を含む）</t>
+          <t>居宅介護支援</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2412,42 +2404,42 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>41883</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0</v>
+        <v>42534</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0</v>
+        <v>47119</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0</v>
+        <v>50595</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>1.125倍</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+          <t>1.208倍</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>居宅サービス</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護（介護予防を含む）</t>
+          <t>居宅介護支援</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2461,42 +2453,42 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0</v>
+        <v>196.7</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0</v>
+        <v>199.6</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0</v>
+        <v>221.4</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0</v>
+        <v>236.9</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>1.126倍</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+          <t>1.204倍</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>介護予防サービス</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>小規模多機能型居宅介護（介護予防を含む）</t>
+          <t>介護予防訪問入浴介護</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2510,238 +2502,238 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>1.207倍</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+          <t>1.237倍</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>介護予防サービス</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>小規模多機能型居宅介護（介護予防を含む）</t>
+          <t>介護予防訪問入浴介護</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
+          <t>回（日）数</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>1.176倍</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>1.235倍</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>介護予防訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
           <t>利用者数</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>地域密着型サービス</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="E43" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>1.250倍</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>1.250倍</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>介護予防訪問看護</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>給付費</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>千円／年</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n">
-        <v>80059</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>81659</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>90923</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>96805</v>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>1.136倍</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>1.209倍</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>地域密着型サービス</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>利用者数</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>1.139倍</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>1.212倍</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+      <c r="E44" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>1.210倍</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>1.235倍</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>地域密着型サービス</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>地域密着型特定施設入居者生活介護</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>給付費</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>千円／年</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>介護予防訪問看護</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>回（日）数</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>1.214倍</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>1.250倍</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>介護予防サービス</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>地域密着型特定施設入居者生活介護</t>
+          <t>介護予防訪問看護</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2755,42 +2747,42 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>1.200倍</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+          <t>1.200倍</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>介護予防サービス</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+          <t>介護予防訪問リハビリテーション</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -2804,238 +2796,238 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>96212</v>
+        <v>2213</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>98336</v>
+        <v>2269</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>106357</v>
+        <v>2551</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>118970</v>
+        <v>2648</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>1.105倍</t>
+          <t>1.153倍</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>1.237倍</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+          <t>1.197倍</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>介護予防サービス</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+          <t>介護予防訪問リハビリテーション</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
+          <t>回（日）数</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>1.153倍</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>1.196倍</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>介護予防訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
           <t>利用者数</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="E48" s="4" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>1.105倍</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>1.237倍</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>地域密着型サービス</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>看護小規模多機能型居宅介護</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="E49" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>1.173倍</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>1.212倍</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>介護予防通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>給付費</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>千円／年</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n">
-        <v>809</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>825</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>858</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>1007</v>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>1.061倍</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>1.245倍</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>地域密着型サービス</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>看護小規模多機能型居宅介護</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>利用者数</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>1.500倍</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>1.500倍</t>
-        </is>
-      </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+      <c r="E50" s="5" t="n">
+        <v>17070</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>17722</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>19141</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>20019</v>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>1.121倍</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>1.173倍</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>施設サービス</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>介護老人福祉施設</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>給付費</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>千円／年</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>232975</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>237772</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>256568</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>288034</v>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>1.101倍</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>1.236倍</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>介護予防通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>回（日）数</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>施設サービス</t>
+          <t>介護予防サービス</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>介護老人福祉施設</t>
+          <t>介護予防通所リハビリテーション</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3049,42 +3041,42 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>67.8</v>
+        <v>34.7</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>69.2</v>
+        <v>35.9</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>74.8</v>
+        <v>39.2</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>83.8</v>
+        <v>40.9</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>1.103倍</t>
+          <t>1.130倍</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>1.236倍</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+          <t>1.179倍</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>施設サービス</t>
+          <t>介護予防サービス</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>介護老人保健施設</t>
+          <t>介護予防短期入所生活介護</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3098,218 +3090,1990 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>260377</v>
+        <v>38</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>265006</v>
+        <v>39</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>288836</v>
+        <v>42</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>318292</v>
+        <v>44</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>1.109倍</t>
+          <t>1.105倍</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>1.222倍</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+          <t>1.158倍</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>介護予防短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>回（日）数</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>1.250倍</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>1.250倍</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>介護予防短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>1.000倍</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>1.000倍</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>介護予防短期入所療養介護（介護老人保健施設）</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>1.111倍</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>1.156倍</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>介護予防短期入所療養介護（介護老人保健施設）</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>回（日）数</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>1.333倍</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>1.333倍</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>介護予防短期入所療養介護（介護老人保健施設）</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>1.000倍</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>1.000倍</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>介護予防福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>3246</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>3366</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>3647</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>3812</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>1.124倍</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>1.174倍</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>介護予防福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>1.128倍</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>1.177倍</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>特定介護予防福祉用具購入費</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>1.100倍</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>1.163倍</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>特定介護予防福祉用具購入費</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>1.500倍</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>1.500倍</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>介護予防住宅改修</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>365</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>407</v>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>1.109倍</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>1.163倍</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>介護予防住宅改修</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>1.333倍</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>1.333倍</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>介護予防認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>4349</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>4538</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>4822</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>5058</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>1.109倍</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>1.163倍</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>介護予防認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>1.143倍</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>1.143倍</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>介護予防支援</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>4610</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>4761</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>5229</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>5452</v>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>1.134倍</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>1.183倍</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>介護予防サービス</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>介護予防支援</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>1.134倍</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>1.182倍</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ver.2.17 で補った欄。** 素案 9-1 では「─」のままで、9-2 の総給付費にだけ入っていた（表の間の範囲の食い違い）。式は上と同じ。算定は calc_chuchoki_R8.10.17.py にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>389</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>437</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>490</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>508</v>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>1.260倍</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>1.306倍</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>1.250倍</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>1.250倍</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>377</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>408</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>457</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>474</v>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>1.212倍</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>1.257倍</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>回（日）数</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>1.207倍</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>1.256倍</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>1.222倍</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>1.333倍</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護（介護予防を含む）</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護（介護予防を含む）</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護（介護予防を含む）</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護（介護予防を含む）</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>80059</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>81659</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>90923</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>96805</v>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>1.136倍</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>1.209倍</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>1.139倍</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>1.212倍</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>96212</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>98336</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>106357</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>118970</v>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>1.105倍</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>1.237倍</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>1.105倍</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>1.237倍</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>看護小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>809</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>825</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>1007</v>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>1.061倍</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>1.245倍</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>看護小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>1.500倍</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>1.500倍</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
           <t>施設サービス</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>232975</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>237772</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>256568</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>288034</v>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>1.101倍</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>1.236倍</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>施設サービス</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>利用者数</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>1.103倍</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>1.236倍</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>施設サービス</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>千円／年</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>260377</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>265006</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>288836</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>318292</v>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>1.109倍</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>1.222倍</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>施設サービス</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>利用者数</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E91" s="4" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F91" s="4" t="n">
         <v>67.7</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G91" s="4" t="n">
         <v>73.90000000000001</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H91" s="4" t="n">
         <v>81.3</v>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="I91" s="4" t="inlineStr">
         <is>
           <t>1.110倍</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J91" s="4" t="inlineStr">
         <is>
           <t>1.221倍</t>
         </is>
       </c>
-      <c r="K54" s="4" t="inlineStr">
+      <c r="K91" s="4" t="inlineStr">
         <is>
           <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>施設サービス</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>介護医療院</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>給付費</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>千円／年</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n">
+      <c r="E92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G55" s="5" t="n">
+      <c r="G92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K92" s="5" t="inlineStr">
         <is>
           <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>施設サービス</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>介護医療院</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>利用者数</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E93" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F93" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G93" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H93" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="I93" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="J93" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
+      <c r="K93" s="4" t="inlineStr">
         <is>
           <t>令和7年度実績×認定者数の伸び（要介護度別）。出所＝介護保険事業状況報告（年報・令和7年度）＋見える化システムの推計値。素案 9-1 の表に同じ値がある</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>介護予防サービス</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>介護予防住宅改修／介護予防支援／介護予防短期入所生活介護／介護予防短期入所療養介護（介護老人保健施設）／介護予防福祉用具貸与／介護予防訪問リハビリテーション／介護予防訪問入浴介護／介護予防訪問看護／介護予防認知症対応型共同生活介護／介護予防通所リハビリテーション／特定介護予防福祉用具購入費</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>給付費</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>千円／年</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="6" t="n"/>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="6" t="n"/>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>─</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>─</t>
-        </is>
-      </c>
-      <c r="K57" s="6" t="inlineStr">
-        <is>
-          <t>⚠ **未実施。** 介護予防給付の11サービスは、サービスごとの長期推計を行っていないため素案でも「─」としている。推測で置かない</t>
         </is>
       </c>
     </row>
@@ -5260,7 +7024,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>内訳の和680,227千円で再現した（検査6）。⚠ 千円未満の丸めにより1千円の差が出る</t>
+          <t>内訳を円で足して一度だけ千円に丸めると680,226千円で、差0で再現した（検査6）</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -7816,7 +9580,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>検査1〜8。適合7件／不適合2件／未実施0件。
+          <t>検査1〜8。適合9件／不適合0件／未実施0件。
 ⚠ **「未実施」を「適合」に丸めていません。**</t>
         </is>
       </c>
@@ -7853,7 +9617,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>検査3　13段階すべてが 乗率×算定Ｂ（6143円）で再現できる</t>
+          <t>検査2　令和17年度　素案 9-1 のサービス別の和1,110,613千円＝9-2 の総給付費1,110,612千円（差+1千円・千円未満の丸めによる）。⚠ **Ver.2.17 で15サービス（94,879千円）を補ったことにより一致した**（Ver.2.16 まではこの分だけ合わなかった）</t>
         </is>
       </c>
     </row>
@@ -7865,7 +9629,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>検査4　年度別の ①＝A＋B／C＝①×23％／J＝C＋D－E が3か年すべてで成り立つ</t>
+          <t>検査2　令和22年度　素案 9-1 のサービス別の和1,218,803千円＝9-2 の総給付費1,218,805千円（差-2千円・千円未満の丸めによる）。⚠ **Ver.2.17 で15サービス（100,997千円）を補ったことにより一致した**（Ver.2.16 まではこの分だけ合わなかった）</t>
         </is>
       </c>
     </row>
@@ -7877,7 +9641,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>検査5　A・B・①・C・D・E・J の3か年計は年度別の合計と一致する</t>
+          <t>検査3　13段階すべてが 乗率×算定Ｂ（6143円）で再現できる</t>
         </is>
       </c>
     </row>
@@ -7889,7 +9653,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>検査6　入所・居住系の給付費　内訳の和680,227千円＝5-5 の記載680,226千円（特定施設入居者生活介護6,255＋介護予防認知症対応型共同生活介護4,349＋認知症対応型共同生活介護80,059＋地域密着型介護老人福祉施設入所者生活介護96,212＋介護老人福祉施設232,975＋介護老人保健施設260,377＋介護医療院0）</t>
+          <t>検査4　年度別の ①＝A＋B／C＝①×23％／J＝C＋D－E が3か年すべてで成り立つ</t>
         </is>
       </c>
     </row>
@@ -7901,7 +9665,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>検査7　2-4 の居宅サービス計の要支援計27,938,709円は、年報の要介護度別明細（要支援1・2の居宅サービス給付費）による。⚠ 要介護度別の内訳は素案 2-4 の表が正本であり、本表では持たない</t>
+          <t>検査5　A・B・①・C・D・E・J の3か年計は年度別の合計と一致する</t>
         </is>
       </c>
     </row>
@@ -7913,31 +9677,31 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
+          <t>検査6　入所・居住系の給付費　内訳を円で足して一度だけ千円に丸めると680,226,353円→680,226千円で、5-5 の記載680,226千円と一致する（介護老人福祉施設232,975,413円＋介護老人保健施設260,376,729円＋地域密着型介護老人福祉施設入所者生活介護96,211,737円＋認知症対応型共同生活介護（介護給付・介護予防）84,407,877円＋特定施設入居者生活介護6,254,597円。⚠ 定期巡回・地域密着型通所介護・看護小規模多機能型は在宅のサービスであり含めない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>検査7　2-4 の居宅サービス計の要支援計27,938,709円は、年報の要介護度別明細（要支援1・2の居宅サービス給付費）による。⚠ 要介護度別の内訳は素案 2-4 の表が正本であり、本表では持たない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>検査8　受託者を主語とする語・他団体の固有名称は15語すべて0件</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>不適合</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>検査2　令和17年度　サービス別の和1,015,734千円と9-2 の総給付費1,110,612千円が合わない（差-94,878千円）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>不適合</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>検査2　令和22年度　サービス別の和1,117,806千円と9-2 の総給付費1,218,805千円が合わない（差-100,999千円）</t>
         </is>
       </c>
     </row>

--- a/kawasaki_project/05_試算・管理シート/川崎町_第10期_計画見込量_中長期・保険料内訳_R8.10.17.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_第10期_計画見込量_中長期・保険料内訳_R8.10.17.xlsx
@@ -13,8 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_保険料の算定" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_3パターンと感度" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_所得段階別の保険料" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_棚卸し70件の対応" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_自己点検" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06b_見える化システムとの差" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_棚卸し70件の対応" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_自己点検" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,7 +55,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +92,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -104,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,6 +130,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6894,6 +6903,382 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>見える化システムの総括表のサービス別の値との差</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>⚠ **総括表の「2_サービス別給付費」には、サービス別の令和17・22年度の給付費が別に入っています。本計画ではこれを用いていません。** 理由は2つです。
+　①令和7年度に給付実績のあるサービスを令和9年度以降0と置いている（10件。確認事項No.76）
+　②令和11年度から令和27年度まで同じ値が並び、認定者数が伸びても給付費が動かない（5件。確認事項No.80の、令和8年5月時点の値が解除できない状態によるもの）
+⚠ **本計画は令和9〜11年度についても総括表のサービス別の値を用いておらず、全年度を通じて年報の実績に認定者数の伸びを乗じる方法で一貫して算定しています。**
+⚠ **県への事前協議で、本計画の数値と見える化システムの出力の違いを問われる可能性があります。** 差を下表に示します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>見える化システムの総括表</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>本計画（素案 9-2）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>差の割合</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>995807</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>1018396</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>-22589</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>-2.22％</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>⚠ **計画期間の中にあり、保険料に効く**</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>998105</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1016634</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>-18529</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>-1.82％</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>⚠ **計画期間の中にあり、保険料に効く**</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1114654</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1110612</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>4042</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>+0.36％</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>長期の見通し。保険料には効かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1220530</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1218805</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1725</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>+0.14％</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>長期の見通し。保険料には効かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>令和7年度に給付実績があるのに令和9年度以降0とされているサービス（確認事項No.76）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>介護予防訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>介護予防短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>介護予防短期入所療養介護（老健）</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>特定介護予防福祉用具購入費</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>介護予防住宅改修</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>特定福祉用具購入費</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>住宅改修費</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>看護小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr"/>
+      <c r="C20" s="9" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>令和11年度から令和27年度まで値が一定のサービス（確認事項No.80）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>介護予防訪問看護</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>介護予防訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>介護予防認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9557,7 +9942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
